--- a/crew_101.xlsx
+++ b/crew_101.xlsx
@@ -459,7 +459,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-07-15 13:01:00</t>
+          <t>Timestamp: 2026-07-15 13:31:00</t>
         </is>
       </c>
     </row>
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>281044</v>
+        <v>283132</v>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
@@ -505,7 +505,7 @@
         </is>
       </c>
       <c r="D4" s="5" t="n">
-        <v>1336</v>
+        <v>1346</v>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
@@ -520,7 +520,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>255134</v>
+        <v>257289</v>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
@@ -528,7 +528,7 @@
         </is>
       </c>
       <c r="D5" s="5" t="n">
-        <v>1217</v>
+        <v>1227</v>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
@@ -543,7 +543,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>246428</v>
+        <v>248114</v>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="D6" s="5" t="n">
-        <v>1174</v>
+        <v>1182</v>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
@@ -566,7 +566,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>358891</v>
+        <v>363087</v>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="D7" s="5" t="n">
-        <v>1708</v>
+        <v>1728</v>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>269603</v>
+        <v>271484</v>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="D8" s="5" t="n">
-        <v>1284</v>
+        <v>1293</v>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
@@ -612,7 +612,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>262612</v>
+        <v>271183</v>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="D9" s="5" t="n">
-        <v>1251</v>
+        <v>1292</v>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>191726</v>
+        <v>203702</v>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="D10" s="5" t="n">
-        <v>914</v>
+        <v>971</v>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>215561</v>
+        <v>225041</v>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="D11" s="5" t="n">
-        <v>1026</v>
+        <v>1071</v>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>187420</v>
+        <v>193309</v>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="D12" s="5" t="n">
-        <v>893</v>
+        <v>921</v>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
@@ -704,7 +704,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>251706</v>
+        <v>253797</v>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>1199</v>
+        <v>1209</v>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>360982</v>
+        <v>369175</v>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="D14" s="5" t="n">
-        <v>1719</v>
+        <v>1758</v>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>304090</v>
+        <v>306183</v>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1448</v>
+        <v>1458</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
@@ -773,7 +773,7 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>259408</v>
+        <v>261535</v>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
         </is>
       </c>
       <c r="D16" s="5" t="n">
-        <v>1164</v>
+        <v>1174</v>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>415797</v>
+        <v>417895</v>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1979</v>
+        <v>1989</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>252962</v>
+        <v>255068</v>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
@@ -827,7 +827,7 @@
         </is>
       </c>
       <c r="D18" s="5" t="n">
-        <v>1133</v>
+        <v>1143</v>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>196721</v>
+        <v>208081</v>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>938</v>
+        <v>992</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>233516</v>
+        <v>235616</v>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="D20" s="5" t="n">
-        <v>1039</v>
+        <v>1049</v>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>499565</v>
+        <v>508560</v>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>2379</v>
+        <v>2422</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>383905</v>
+        <v>389155</v>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         </is>
       </c>
       <c r="D22" s="5" t="n">
-        <v>1827</v>
+        <v>1852</v>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>247205</v>
+        <v>249314</v>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>1104</v>
+        <v>1114</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>291903</v>
+        <v>294015</v>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         </is>
       </c>
       <c r="D25" s="5" t="n">
-        <v>1389</v>
+        <v>1399</v>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>155764</v>
+        <v>157820</v>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="D26" s="5" t="n">
-        <v>742</v>
+        <v>752</v>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>441965</v>
+        <v>446142</v>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="D28" s="5" t="n">
-        <v>2104</v>
+        <v>2124</v>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
@@ -1072,7 +1072,7 @@
         </is>
       </c>
       <c r="B29" s="5" t="n">
-        <v>216922</v>
+        <v>219290</v>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         </is>
       </c>
       <c r="D29" s="5" t="n">
-        <v>1033</v>
+        <v>1044</v>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>274715</v>
+        <v>276815</v>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         </is>
       </c>
       <c r="D30" s="5" t="n">
-        <v>1308</v>
+        <v>1318</v>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>238845</v>
+        <v>240943</v>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         </is>
       </c>
       <c r="D31" s="5" t="n">
-        <v>1063</v>
+        <v>1073</v>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>338230</v>
+        <v>346585</v>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="D32" s="5" t="n">
-        <v>1609</v>
+        <v>1649</v>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>303643</v>
+        <v>310961</v>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="D33" s="5" t="n">
-        <v>1448</v>
+        <v>1483</v>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>312137</v>
+        <v>314224</v>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
         </is>
       </c>
       <c r="D34" s="5" t="n">
-        <v>1487</v>
+        <v>1497</v>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>259338</v>
+        <v>261413</v>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         </is>
       </c>
       <c r="D35" s="5" t="n">
-        <v>1236</v>
+        <v>1246</v>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>409820</v>
+        <v>411906</v>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="D36" s="5" t="n">
-        <v>1946</v>
+        <v>1956</v>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         </is>
       </c>
       <c r="B37" s="5" t="n">
-        <v>320075</v>
+        <v>322157</v>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         </is>
       </c>
       <c r="D37" s="5" t="n">
-        <v>1524</v>
+        <v>1534</v>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>379911</v>
+        <v>389847</v>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         </is>
       </c>
       <c r="D38" s="5" t="n">
-        <v>1799</v>
+        <v>1846</v>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>418732</v>
+        <v>421902</v>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="D39" s="5" t="n">
-        <v>1994</v>
+        <v>2009</v>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>269485</v>
+        <v>278044</v>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         </is>
       </c>
       <c r="D40" s="5" t="n">
-        <v>1282</v>
+        <v>1323</v>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         </is>
       </c>
       <c r="B41" s="5" t="n">
-        <v>312656</v>
+        <v>316713</v>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         </is>
       </c>
       <c r="D41" s="5" t="n">
-        <v>1490</v>
+        <v>1509</v>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="B42" s="5" t="n">
-        <v>231076</v>
+        <v>233172</v>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="D42" s="5" t="n">
-        <v>1028</v>
+        <v>1038</v>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>

--- a/crew_101.xlsx
+++ b/crew_101.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="2026-07-15" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="2026-07-16" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1417,4 +1418,990 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Crew: Shad0w Ninjas (101)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-07-16 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Dmg</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Dmg</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Boss Kills</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Kills</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>dogan</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>448708</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>+165576</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>2134</v>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>I Am Dead  @_@</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>356048</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>+98759</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>1697</v>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Yata</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>331994</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>+83880</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>1582</v>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>AangEX</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>516348</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>+153261</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>2458</v>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Feirisu</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>437820</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>+166336</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>2086</v>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Wolf †</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>424481</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>+153298</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>2021</v>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>MATHEMATRICK</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>228266</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>+24564</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>1088</v>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>BlacKAkiresu O</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>367206</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>+142165</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>1748</v>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Tuyu|Fortuners</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>375185</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>+181876</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>1786</v>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Khakashi Hatake</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>340858</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>+87061</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>1624</v>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ikhram </t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>567835</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>+198660</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>2703</v>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Prince G™</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>389013</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>+82830</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>1852</v>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Yhwach Genryusai</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>349977</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>+88442</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>1596</v>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>NicolasRicko</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>485363</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>+67468</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>2310</v>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Izx Hatake Jr</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>340778</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>+85710</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>1551</v>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>ASHBORN™</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>272747</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>+64666</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heisenberg </t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>321443</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>+85827</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>1458</v>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Tobirama Senju™</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>657944</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>+149384</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>3133</v>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>ZenithEX</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>630629</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>+241474</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>3002</v>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>§åñÐåïmårµ | Frtners</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>337564</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>+88250</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>1534</v>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Meru™</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>612668</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>+182961</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>2918</v>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Vnzla Anbu |SN</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>373245</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>+79230</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>1776</v>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Signature</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>236736</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>+78916</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>1128</v>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Fusion</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>416120</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>+85068</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>1984</v>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Sesshomaru</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>590191</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>+144049</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>2809</v>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>KYO</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>297978</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>+78688</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>1418</v>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>SL41F3RT</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>408518</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>+131703</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>1945</v>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Lovebird | Gorelax</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>329669</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>+88726</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>1495</v>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>ShadowRavenX</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>547330</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>+200745</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>2605</v>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>SNC | TemperiTa</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>569916</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>+258955</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>2716</v>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>SmallDino</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>459836</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>+145612</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>2190</v>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>Breaker LITE</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>360091</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>+98678</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>1716</v>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Snoopy | Kokyotosu</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>544177</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>+132271</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>2586</v>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Arya</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>403896</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>+81739</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>1923</v>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Morrissey</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>710626</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>+320779</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="n">
+        <v>3373</v>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Jonny Brown</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>659024</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>+237122</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="n">
+        <v>3138</v>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Knightwalker</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>423335</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>+145291</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="n">
+        <v>2016</v>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a fucking ninja </t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>390932</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>+74219</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>1862</v>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Izx Infernity </t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>318674</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>+85502</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="n">
+        <v>1445</v>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Erza Scarlet</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>474739</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>2255</v>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/crew_101.xlsx
+++ b/crew_101.xlsx
@@ -1446,7 +1446,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-07-16 13:01:00</t>
+          <t>Timestamp: 2026-07-16 13:31:00</t>
         </is>
       </c>
     </row>
@@ -1484,19 +1484,19 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>448708</v>
+        <v>450780</v>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>+165576</t>
+          <t>+167648</t>
         </is>
       </c>
       <c r="D4" s="5" t="n">
-        <v>2134</v>
+        <v>2144</v>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+798</t>
         </is>
       </c>
     </row>
@@ -1507,19 +1507,19 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>356048</v>
+        <v>358168</v>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>+98759</t>
+          <t>+100879</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
-        <v>1697</v>
+        <v>1707</v>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+480</t>
         </is>
       </c>
     </row>
@@ -1530,19 +1530,19 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>331994</v>
+        <v>347214</v>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>+83880</t>
+          <t>+99100</t>
         </is>
       </c>
       <c r="D6" s="5" t="n">
-        <v>1582</v>
+        <v>1655</v>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+473</t>
         </is>
       </c>
     </row>
@@ -1553,19 +1553,19 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>516348</v>
+        <v>518454</v>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>+153261</t>
+          <t>+155367</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
-        <v>2458</v>
+        <v>2468</v>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+740</t>
         </is>
       </c>
     </row>
@@ -1576,19 +1576,19 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>437820</v>
+        <v>439923</v>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>+166336</t>
+          <t>+168439</t>
         </is>
       </c>
       <c r="D8" s="5" t="n">
-        <v>2086</v>
+        <v>2096</v>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+803</t>
         </is>
       </c>
     </row>
@@ -1599,19 +1599,19 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>424481</v>
+        <v>426595</v>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>+153298</t>
+          <t>+155412</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
-        <v>2021</v>
+        <v>2031</v>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+739</t>
         </is>
       </c>
     </row>
@@ -1622,19 +1622,19 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>228266</v>
+        <v>228484</v>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>+24564</t>
+          <t>+24782</t>
         </is>
       </c>
       <c r="D10" s="5" t="n">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+118</t>
         </is>
       </c>
     </row>
@@ -1645,19 +1645,19 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>367206</v>
+        <v>369288</v>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>+142165</t>
+          <t>+144247</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
-        <v>1748</v>
+        <v>1758</v>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+687</t>
         </is>
       </c>
     </row>
@@ -1668,19 +1668,19 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>375185</v>
+        <v>375810</v>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>+181876</t>
+          <t>+182501</t>
         </is>
       </c>
       <c r="D12" s="5" t="n">
-        <v>1786</v>
+        <v>1789</v>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+868</t>
         </is>
       </c>
     </row>
@@ -1691,19 +1691,19 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>340858</v>
+        <v>356812</v>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>+87061</t>
+          <t>+103015</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>1624</v>
+        <v>1700</v>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+491</t>
         </is>
       </c>
     </row>
@@ -1714,19 +1714,19 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>567835</v>
+        <v>569898</v>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>+198660</t>
+          <t>+200723</t>
         </is>
       </c>
       <c r="D14" s="5" t="n">
-        <v>2703</v>
+        <v>2713</v>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+955</t>
         </is>
       </c>
     </row>
@@ -1737,19 +1737,19 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>389013</v>
+        <v>391092</v>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>+82830</t>
+          <t>+84909</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1852</v>
+        <v>1862</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+404</t>
         </is>
       </c>
     </row>
@@ -1760,19 +1760,19 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>349977</v>
+        <v>352067</v>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>+88442</t>
+          <t>+90532</t>
         </is>
       </c>
       <c r="D16" s="5" t="n">
-        <v>1596</v>
+        <v>1606</v>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+432</t>
         </is>
       </c>
     </row>
@@ -1783,19 +1783,19 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>485363</v>
+        <v>487503</v>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>+67468</t>
+          <t>+69608</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>2310</v>
+        <v>2320</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+331</t>
         </is>
       </c>
     </row>
@@ -1806,19 +1806,19 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>340778</v>
+        <v>342881</v>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>+85710</t>
+          <t>+87813</t>
         </is>
       </c>
       <c r="D18" s="5" t="n">
-        <v>1551</v>
+        <v>1561</v>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+418</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+308</t>
         </is>
       </c>
     </row>
@@ -1852,19 +1852,19 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>321443</v>
+        <v>323523</v>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>+85827</t>
+          <t>+87907</t>
         </is>
       </c>
       <c r="D20" s="5" t="n">
-        <v>1458</v>
+        <v>1468</v>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+419</t>
         </is>
       </c>
     </row>
@@ -1875,19 +1875,19 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>657944</v>
+        <v>666988</v>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>+149384</t>
+          <t>+158428</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>3133</v>
+        <v>3176</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+754</t>
         </is>
       </c>
     </row>
@@ -1898,19 +1898,19 @@
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>630629</v>
+        <v>631056</v>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>+241474</t>
+          <t>+241901</t>
         </is>
       </c>
       <c r="D22" s="5" t="n">
-        <v>3002</v>
+        <v>3004</v>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+1152</t>
         </is>
       </c>
     </row>
@@ -1921,19 +1921,19 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>337564</v>
+        <v>339664</v>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>+88250</t>
+          <t>+90350</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>1534</v>
+        <v>1544</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+430</t>
         </is>
       </c>
     </row>
@@ -1944,19 +1944,19 @@
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>612668</v>
+        <v>623186</v>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>+182961</t>
+          <t>+193479</t>
         </is>
       </c>
       <c r="D24" s="5" t="n">
-        <v>2918</v>
+        <v>2968</v>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+920</t>
         </is>
       </c>
     </row>
@@ -1967,19 +1967,19 @@
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>373245</v>
+        <v>375328</v>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>+79230</t>
+          <t>+81313</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
-        <v>1776</v>
+        <v>1786</v>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+387</t>
         </is>
       </c>
     </row>
@@ -2002,7 +2002,7 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+376</t>
         </is>
       </c>
     </row>
@@ -2013,19 +2013,19 @@
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>416120</v>
+        <v>418210</v>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>+85068</t>
+          <t>+87158</t>
         </is>
       </c>
       <c r="D27" s="5" t="n">
-        <v>1984</v>
+        <v>1994</v>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+415</t>
         </is>
       </c>
     </row>
@@ -2036,19 +2036,19 @@
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>590191</v>
+        <v>597746</v>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>+144049</t>
+          <t>+151604</t>
         </is>
       </c>
       <c r="D28" s="5" t="n">
-        <v>2809</v>
+        <v>2845</v>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+721</t>
         </is>
       </c>
     </row>
@@ -2059,19 +2059,19 @@
         </is>
       </c>
       <c r="B29" s="5" t="n">
-        <v>297978</v>
+        <v>300058</v>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>+78688</t>
+          <t>+80768</t>
         </is>
       </c>
       <c r="D29" s="5" t="n">
-        <v>1418</v>
+        <v>1428</v>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+384</t>
         </is>
       </c>
     </row>
@@ -2082,19 +2082,19 @@
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>408518</v>
+        <v>410635</v>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>+131703</t>
+          <t>+133820</t>
         </is>
       </c>
       <c r="D30" s="5" t="n">
-        <v>1945</v>
+        <v>1955</v>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+637</t>
         </is>
       </c>
     </row>
@@ -2105,19 +2105,19 @@
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>329669</v>
+        <v>331781</v>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>+88726</t>
+          <t>+90838</t>
         </is>
       </c>
       <c r="D31" s="5" t="n">
-        <v>1495</v>
+        <v>1505</v>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+432</t>
         </is>
       </c>
     </row>
@@ -2128,19 +2128,19 @@
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>547330</v>
+        <v>557245</v>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>+200745</t>
+          <t>+210660</t>
         </is>
       </c>
       <c r="D32" s="5" t="n">
-        <v>2605</v>
+        <v>2652</v>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+1003</t>
         </is>
       </c>
     </row>
@@ -2151,19 +2151,19 @@
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>569916</v>
+        <v>577650</v>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>+258955</t>
+          <t>+266689</t>
         </is>
       </c>
       <c r="D33" s="5" t="n">
-        <v>2716</v>
+        <v>2753</v>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+1270</t>
         </is>
       </c>
     </row>
@@ -2174,19 +2174,19 @@
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>459836</v>
+        <v>461976</v>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>+145612</t>
+          <t>+147752</t>
         </is>
       </c>
       <c r="D34" s="5" t="n">
-        <v>2190</v>
+        <v>2200</v>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+703</t>
         </is>
       </c>
     </row>
@@ -2197,19 +2197,19 @@
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>360091</v>
+        <v>362181</v>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>+98678</t>
+          <t>+100768</t>
         </is>
       </c>
       <c r="D35" s="5" t="n">
-        <v>1716</v>
+        <v>1726</v>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+480</t>
         </is>
       </c>
     </row>
@@ -2220,19 +2220,19 @@
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>544177</v>
+        <v>546302</v>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>+132271</t>
+          <t>+134396</t>
         </is>
       </c>
       <c r="D36" s="5" t="n">
-        <v>2586</v>
+        <v>2596</v>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+640</t>
         </is>
       </c>
     </row>
@@ -2255,7 +2255,7 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+389</t>
         </is>
       </c>
     </row>
@@ -2266,19 +2266,19 @@
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>710626</v>
+        <v>720770</v>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>+320779</t>
+          <t>+330923</t>
         </is>
       </c>
       <c r="D38" s="5" t="n">
-        <v>3373</v>
+        <v>3421</v>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+1575</t>
         </is>
       </c>
     </row>
@@ -2289,19 +2289,19 @@
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>659024</v>
+        <v>664066</v>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>+237122</t>
+          <t>+242164</t>
         </is>
       </c>
       <c r="D39" s="5" t="n">
-        <v>3138</v>
+        <v>3162</v>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+1153</t>
         </is>
       </c>
     </row>
@@ -2312,19 +2312,19 @@
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>423335</v>
+        <v>425446</v>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>+145291</t>
+          <t>+147402</t>
         </is>
       </c>
       <c r="D40" s="5" t="n">
-        <v>2016</v>
+        <v>2026</v>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+703</t>
         </is>
       </c>
     </row>
@@ -2335,19 +2335,19 @@
         </is>
       </c>
       <c r="B41" s="5" t="n">
-        <v>390932</v>
+        <v>393229</v>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>+74219</t>
+          <t>+76516</t>
         </is>
       </c>
       <c r="D41" s="5" t="n">
-        <v>1862</v>
+        <v>1873</v>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+364</t>
         </is>
       </c>
     </row>
@@ -2358,19 +2358,19 @@
         </is>
       </c>
       <c r="B42" s="5" t="n">
-        <v>318674</v>
+        <v>320768</v>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>+85502</t>
+          <t>+87596</t>
         </is>
       </c>
       <c r="D42" s="5" t="n">
-        <v>1445</v>
+        <v>1455</v>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+417</t>
         </is>
       </c>
     </row>
@@ -2393,7 +2393,7 @@
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0</t>
         </is>
       </c>
     </row>

--- a/crew_101.xlsx
+++ b/crew_101.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="2026-07-15" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="2026-07-16" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="2026-07-17" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -453,7 +454,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Crew: Shad0w Ninjas (101)</t>
+          <t>Crew: Shad0w Ninjas (101) | S28 P1</t>
         </is>
       </c>
     </row>
@@ -1439,7 +1440,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Crew: Shad0w Ninjas (101)</t>
+          <t>Crew: Shad0w Ninjas (101) | S28 P1</t>
         </is>
       </c>
     </row>
@@ -2394,6 +2395,992 @@
       <c r="E43" s="5" t="inlineStr">
         <is>
           <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Crew: Shad0w Ninjas (101) | S28 P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-07-17 13:54:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Dmg</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Dmg</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Boss Kills</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Kills</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>dogan</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>564414</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>+113634</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>2686</v>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>+1340</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>I Am Dead  @_@</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>470583</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>+112415</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>2243</v>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>+1016</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Yata</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>409315</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>+62101</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>1950</v>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>+768</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>AangEX</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>597511</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>+79057</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>2843</v>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>+1115</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Feirisu</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>538917</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>+98994</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>2568</v>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>+1275</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Wolf †</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>559389</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>+132794</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>2664</v>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>+1372</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>MATHEMATRICK</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>366580</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>+138096</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>1744</v>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>+773</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>BlacKAkiresu O</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>495976</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>+126688</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>2363</v>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>+1292</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Tuyu|Fortuners</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>425446</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>+49636</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>+1104</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Khakashi Hatake</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>439157</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>+82345</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>2093</v>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>+884</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ikhram </t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>648397</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>+78499</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>3087</v>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>+1329</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Prince G™</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>510702</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>+119610</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>2432</v>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>+974</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Yhwach Genryusai</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>447435</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>+95368</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>2060</v>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>+886</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>NicolasRicko</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>577151</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>+89648</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>2746</v>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>+757</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Izx Hatake Jr</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>438134</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>+95253</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>2015</v>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>+872</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>ASHBORN™</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>406129</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>+133382</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>1935</v>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>+943</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heisenberg </t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>417623</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>+94100</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>1915</v>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>+866</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Tobirama Senju™</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>870033</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>+203045</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>4142</v>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>+1720</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>ZenithEX</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>693857</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>+62801</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>3304</v>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>+1452</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>§åñÐåïmårµ | Frtners</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>431791</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>+92127</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>1984</v>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>+870</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Meru™</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>778313</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>+155127</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>3708</v>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>+1660</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Vnzla Anbu |SN</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>490096</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>+114768</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>2332</v>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>+933</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Signature</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>367520</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>+130784</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>1751</v>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>+999</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Fusion</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>532815</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>+114605</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>2540</v>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>+961</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Sesshomaru</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>1094457</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>+496711</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>5213</v>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>+3089</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>KYO</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>359434</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>+59376</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>1711</v>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>+667</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>SL41F3RT</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>524904</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>+114269</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>2499</v>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>+1181</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Lovebird | Gorelax</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>426622</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>+94841</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>1958</v>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>+885</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>ShadowRavenX</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>725307</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>+168062</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>3453</v>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>+1804</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>SNC | TemperiTa</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>728743</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>+151093</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>3472</v>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>+1989</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>SmallDino</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>583883</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>+121907</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>2780</v>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>+1283</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>Breaker LITE</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>498017</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>+135836</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>2372</v>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>+1126</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Snoopy | Kokyotosu</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>608719</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>+62417</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>2893</v>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>+937</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Arya</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>465908</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>+62012</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>2218</v>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>+684</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Morrissey</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>874965</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>+154195</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="n">
+        <v>4154</v>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>+2308</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Jonny Brown</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>785318</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>+121252</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="n">
+        <v>3738</v>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>+1729</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Knightwalker</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>560125</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>+134679</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="n">
+        <v>2666</v>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>+1343</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a fucking ninja </t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>494009</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>+100780</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>2353</v>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>+844</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Izx Infernity </t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>414328</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>+93560</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="n">
+        <v>1901</v>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>+863</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Erza Scarlet</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>660684</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>+185945</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>3141</v>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>+886</t>
         </is>
       </c>
     </row>

--- a/crew_101.xlsx
+++ b/crew_101.xlsx
@@ -10,6 +10,7 @@
     <sheet name="2026-07-15" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="2026-07-16" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="2026-07-17" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="2026-07-18" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3391,4 +3392,990 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Crew: Shad0w Ninjas (101) | S28 P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-07-18 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Dmg</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Dmg</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Boss Kills</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Kills</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>dogan</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>680359</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>+115945</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>3238</v>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>+1094</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>I Am Dead  @_@</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>586316</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>+115733</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>2794</v>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>+1087</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Yata</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>505190</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>+95875</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>2407</v>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>+752</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>AangEX</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>713541</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>+116030</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>3396</v>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>+928</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Feirisu</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>652017</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>+113100</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>3107</v>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>+1011</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Wolf †</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>677046</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>+117657</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>3224</v>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>+1193</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>MATHEMATRICK</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>517876</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>+151296</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>2466</v>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>+1377</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>BlacKAkiresu O</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>614959</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>+118983</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>2930</v>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>+1172</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Tuyu|Fortuners</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>506241</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>+80795</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>2410</v>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>+621</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Khakashi Hatake</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>535394</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>+96237</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>2552</v>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>+852</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ikhram </t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>737511</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>+89114</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>3511</v>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>+798</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Prince G™</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>627036</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>+116334</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>2987</v>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>+1125</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Yhwach Genryusai</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>557217</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>+109782</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>2583</v>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>+977</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>NicolasRicko</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>664827</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>+87676</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>3164</v>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>+844</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Izx Hatake Jr</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>531348</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>+93214</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>2459</v>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>+898</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>ASHBORN™</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>475617</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>+69488</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>2266</v>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>+966</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heisenberg </t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>527358</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>+109735</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>2438</v>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>+970</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Tobirama Senju™</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>977946</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>+107913</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>4656</v>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>+1480</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>ZenithEX</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>790123</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>+96266</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>3762</v>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>+758</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>§åñÐåïmårµ | Frtners</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>540445</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>+108654</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>2501</v>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>+957</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Meru™</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>871787</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>+93474</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>4153</v>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>+1185</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Vnzla Anbu |SN</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>606316</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>+116220</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>2886</v>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>+1100</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Signature</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>510389</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>+142869</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>2430</v>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>+1302</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Fusion</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>648816</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>+116001</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>3092</v>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>+1098</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Sesshomaru</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>1284632</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>+190175</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>6118</v>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>+3273</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>KYO</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>457246</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>+97812</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>2177</v>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>+749</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>SL41F3RT</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>640814</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>+115910</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>3051</v>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>+1096</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Lovebird | Gorelax</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>536249</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>+109627</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>2480</v>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>+975</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>ShadowRavenX</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>812904</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>+87597</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>3870</v>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>+1218</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>SNC | TemperiTa</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>816842</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>+88099</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>3890</v>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>+1137</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>SmallDino</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>682486</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>+98603</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>3249</v>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>+1049</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>Breaker LITE</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>613941</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>+115924</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>2924</v>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>+1198</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Snoopy | Kokyotosu</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>754633</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>+145914</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>3588</v>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>+992</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Arya</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>637942</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>+172034</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>3036</v>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>+1113</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Morrissey</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>990625</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>+115660</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="n">
+        <v>4704</v>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>+1283</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Jonny Brown</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>896666</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>+111348</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="n">
+        <v>4268</v>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>+1106</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Knightwalker</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>674442</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>+114317</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="n">
+        <v>3211</v>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>+1185</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a fucking ninja </t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>637433</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>+143424</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>3036</v>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>+1163</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Izx Infernity </t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>521534</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>+107206</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="n">
+        <v>2412</v>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>+957</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Erza Scarlet</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>660684</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>3141</v>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>+886</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/crew_101.xlsx
+++ b/crew_101.xlsx
@@ -11,6 +11,7 @@
     <sheet name="2026-07-16" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="2026-07-17" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="2026-07-18" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="2026-07-19" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4378,4 +4379,658 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Crew: Shad0w Ninjas (101) | S28 P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-07-19 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Dmg</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Dmg</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>dogan</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>750938</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>+70579</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>I Am Dead  @_@</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>734277</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>+147961</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Yata</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>548486</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>+43296</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>AangEX</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>821854</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>+108313</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Feirisu</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>719963</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>+67946</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Wolf †</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>760407</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>+83361</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>MATHEMATRICK</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>642220</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>+124344</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>BlacKAkiresu O</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>667956</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>+52997</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Tuyu|Fortuners</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>590218</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>+83977</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Khakashi Hatake</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>585884</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>+50490</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ikhram </t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>830337</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>+92826</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Prince G™</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>712822</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>+85786</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Yhwach Genryusai</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>600053</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>+42836</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>NicolasRicko</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>756666</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>+91839</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Izx Hatake Jr</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>574197</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>+42849</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>ASHBORN™</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>543598</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>+67981</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heisenberg </t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>570182</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>+42824</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Tobirama Senju™</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>1010778</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>+32832</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>ZenithEX</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>871945</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>+81822</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>§åñÐåïmårµ | Frtners</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>583280</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>+42835</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Meru™</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>871787</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Vnzla Anbu |SN</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>714457</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>+108141</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Signature</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>639488</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>+129099</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Fusion</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>752188</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>+103372</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Sesshomaru</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>1373266</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>+88634</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>KYO</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>503263</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>+46017</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>SL41F3RT</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>696672</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>+55858</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Lovebird | Gorelax</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>579158</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>+42909</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>ShadowRavenX</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>904362</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>+91458</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>SNC | TemperiTa</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>908740</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>+91898</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>SmallDino</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>765859</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>+83373</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>Breaker LITE</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>722634</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>+108693</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Snoopy | Kokyotosu</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>797170</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>+42537</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Arya</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>832940</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>+194998</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Morrissey</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>1098120</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>+107495</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Jonny Brown</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>997467</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>+100801</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Knightwalker</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>760055</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>+85613</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a fucking ninja </t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>696753</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>+59320</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Izx Infernity </t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>564491</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>+42957</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Erza Scarlet</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>841211</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>+180527</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/crew_101.xlsx
+++ b/crew_101.xlsx
@@ -12,6 +12,7 @@
     <sheet name="2026-07-17" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="2026-07-18" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="2026-07-19" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="2026-07-20" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -5033,4 +5034,990 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Crew: Shad0w Ninjas (101) | S28 P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-07-20 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Dmg</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Dmg</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Boss Kills</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Kills</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>dogan</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>750938</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>3574</v>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>+336</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>I Am Dead  @_@</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>734277</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>3498</v>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>+704</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Yata</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>548486</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>2612</v>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>+205</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>AangEX</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>821854</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>3911</v>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>+515</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Feirisu</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>719963</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>3431</v>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>+324</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Wolf †</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>760407</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>3621</v>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>+397</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>MATHEMATRICK</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>642520</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>+300</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>3058</v>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>+592</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>BlacKAkiresu O</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>667956</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>3182</v>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>+252</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Tuyu|Fortuners</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>612771</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>+22553</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>2810</v>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>+400</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Khakashi Hatake</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>585884</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>2792</v>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>+240</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ikhram </t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>830337</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>3954</v>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>+443</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Prince G™</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>712822</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>3395</v>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>+408</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Yhwach Genryusai</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>600053</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>2787</v>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>+204</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>NicolasRicko</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>756666</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>3601</v>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>+437</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Izx Hatake Jr</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>574197</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>2663</v>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>+204</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>ASHBORN™</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>543900</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>+302</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>2589</v>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>+323</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heisenberg </t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>570182</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>2642</v>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>+204</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Tobirama Senju™</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>1076288</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>+65510</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>4812</v>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>+156</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>ZenithEX</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>871945</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>4152</v>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>+390</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>§åñÐåïmårµ | Frtners</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>583280</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>2705</v>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>+204</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Meru™</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>871787</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>4153</v>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Vnzla Anbu |SN</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>818429</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>+103972</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>3400</v>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>+514</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Signature</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>639656</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>+168</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>3044</v>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>+614</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Fusion</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>752188</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>3584</v>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>+492</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Sesshomaru</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>1373266</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>6539</v>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>+421</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>KYO</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>503263</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>2396</v>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>+219</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>SL41F3RT</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>696672</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>3317</v>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>+266</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Lovebird | Gorelax</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>579158</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>2684</v>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>+204</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>ShadowRavenX</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>904362</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>4305</v>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>+435</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>SNC | TemperiTa</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>908740</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>4328</v>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>+438</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>SmallDino</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>768068</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>+2209</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>3646</v>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>+397</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>Breaker LITE</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>825821</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>+103187</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>3440</v>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>+516</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Snoopy | Kokyotosu</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>797170</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>3791</v>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>+203</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Arya</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>832940</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>3964</v>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>+928</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Morrissey</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>1108526</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>+10406</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="n">
+        <v>5216</v>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>+512</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Jonny Brown</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>1085303</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>+87836</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="n">
+        <v>4749</v>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>+481</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Knightwalker</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>760055</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="n">
+        <v>3619</v>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>+408</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a fucking ninja </t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>696753</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>3319</v>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>+283</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Izx Infernity </t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>564491</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="n">
+        <v>2616</v>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>+204</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Erza Scarlet</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>841211</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>4000</v>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>+859</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/crew_101.xlsx
+++ b/crew_101.xlsx
@@ -13,6 +13,7 @@
     <sheet name="2026-07-18" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="2026-07-19" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="2026-07-20" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="2026-07-21" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -6020,4 +6021,990 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Crew: Shad0w Ninjas (101) | S28 P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-07-21 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Dmg</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Dmg</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Boss Kills</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Kills</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>dogan</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>750938</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>3574</v>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>+3574</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>I Am Dead  @_@</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>734277</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>3498</v>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>+3498</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Yata</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>548486</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>2612</v>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>+2612</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>AangEX</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>821854</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>3911</v>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>+3911</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Feirisu</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>719963</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>3431</v>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>+3431</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Wolf †</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>760407</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>3621</v>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>+3621</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>MATHEMATRICK</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>642520</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>3058</v>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>+3058</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>BlacKAkiresu O</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>667956</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>3182</v>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>+3182</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Tuyu|Fortuners</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>639662</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>+26891</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>2810</v>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>+2810</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Khakashi Hatake</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>585884</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>2792</v>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>+2792</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ikhram </t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>830337</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>3954</v>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>+3954</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Prince G™</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>728582</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>+15760</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>3395</v>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>+3395</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Yhwach Genryusai</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>600053</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>2787</v>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>+2787</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>NicolasRicko</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>756666</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>3601</v>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>+3601</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Izx Hatake Jr</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>574197</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>2663</v>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>+2663</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>ASHBORN™</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>543900</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>2589</v>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>+2589</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heisenberg </t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>570182</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>2642</v>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>+2642</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Tobirama Senju™</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>1142294</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>+66006</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>4812</v>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>+4812</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>ZenithEX</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>871945</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>4152</v>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>+4152</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>§åñÐåïmårµ | Frtners</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>583280</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>2705</v>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>+2705</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Meru™</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>871787</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>4153</v>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>+4153</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Vnzla Anbu |SN</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>885699</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>+67270</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>3400</v>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>+3400</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Signature</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>639656</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>3044</v>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>+3044</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Fusion</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>752188</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>3584</v>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>+3584</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Sesshomaru</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>1381295</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>+8029</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>6539</v>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>+6539</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>KYO</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>503263</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>2396</v>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>+2396</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>SL41F3RT</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>696672</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>3317</v>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>+3317</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>579158</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>2684</v>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>ShadowRavenX</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>904362</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>4305</v>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>+4305</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>SNC | TemperiTa</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>908740</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>4328</v>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>+4328</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>SmallDino</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>768068</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>3646</v>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>+3646</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>Breaker LITE</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>925594</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>+99773</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>3440</v>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>+3440</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Snoopy | Kokyotosu</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>797170</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>3791</v>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>+3791</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Arya</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>832940</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>3964</v>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>+3964</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Morrissey</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>1108526</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="n">
+        <v>5216</v>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>+5216</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Jonny Brown</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>1135408</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>+50105</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="n">
+        <v>4749</v>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>+4749</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Knightwalker</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>764541</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>+4486</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="n">
+        <v>3619</v>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>+3619</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a fucking ninja </t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>696753</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>3319</v>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>+3319</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Izx Infernity </t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>564491</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="n">
+        <v>2616</v>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>+2616</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Erza Scarlet</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>841211</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>4000</v>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>+4000</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/crew_101.xlsx
+++ b/crew_101.xlsx
@@ -14,6 +14,7 @@
     <sheet name="2026-07-19" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="2026-07-20" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="2026-07-21" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="2026-07-22" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -7007,4 +7008,990 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Crew: Shad0w Ninjas (101) | S28 P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-07-22 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Dmg</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Dmg</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Boss Kills</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Kills</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>dogan</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>750938</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>3574</v>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>I Am Dead  @_@</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>734448</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>+171</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>3498</v>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Yata</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>548486</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>2612</v>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>AangEX</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>821854</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>3911</v>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Feirisu</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>719963</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>3431</v>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Wolf †</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>760407</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>3621</v>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>MATHEMATRICK</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>642520</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>3058</v>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>BlacKAkiresu O</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>667956</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>3182</v>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Tuyu|Fortuners</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>678011</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>+38349</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>2810</v>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Khakashi Hatake</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>585884</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>2792</v>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ikhram </t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>830337</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>3954</v>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Prince G™</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>742430</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>+13848</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>3395</v>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Yhwach Genryusai</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>600053</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>2787</v>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>NicolasRicko</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>756666</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>3601</v>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Izx Hatake Jr</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>574197</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>2663</v>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>ASHBORN™</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>543900</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>2589</v>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heisenberg </t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>570182</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>2642</v>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Tobirama Senju™</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>1228794</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>+86500</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>4812</v>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>ZenithEX</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>871945</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>4152</v>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>§åñÐåïmårµ | Frtners</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>583280</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>2705</v>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Meru™</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>871787</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>4153</v>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Vnzla Anbu |SN</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>965973</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>+80274</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>3400</v>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Signature</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>639656</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>3044</v>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Fusion</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>752188</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>3584</v>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Sesshomaru</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>1386562</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>+5267</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>6539</v>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>KYO</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>503263</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>2396</v>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>SL41F3RT</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>696672</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>3317</v>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>579158</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>2684</v>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>ShadowRavenX</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>904362</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>4305</v>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>SNC | TemperiTa</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>908740</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>4328</v>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>SmallDino</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>768068</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>3646</v>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>Breaker LITE</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>1029384</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>+103790</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>3440</v>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Snoopy | Kokyotosu</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>797170</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>3791</v>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Arya</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>832940</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>3964</v>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Morrissey</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>1112614</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>+4088</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="n">
+        <v>5216</v>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Jonny Brown</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>1195284</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>+59876</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="n">
+        <v>4749</v>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Knightwalker</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>766062</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>+1521</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="n">
+        <v>3619</v>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a fucking ninja </t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>701323</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>+4570</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>3319</v>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Izx Infernity </t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>564491</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="n">
+        <v>2616</v>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Erza Scarlet</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>841211</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>4000</v>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/crew_101.xlsx
+++ b/crew_101.xlsx
@@ -15,6 +15,7 @@
     <sheet name="2026-07-20" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="2026-07-21" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="2026-07-22" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="2026-07-23" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -7994,4 +7995,990 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Crew: Shad0w Ninjas (101) | S28 P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-07-23 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Dmg</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Dmg</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Boss Kills</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Kills</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>dogan</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>750938</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>3574</v>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>I Am Dead  @_@</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>734448</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>3498</v>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Yata</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>548486</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>2612</v>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>AangEX</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>821854</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>3911</v>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Feirisu</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>719963</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>3431</v>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Wolf †</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>760407</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>3621</v>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>MATHEMATRICK</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>642520</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>3058</v>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>BlacKAkiresu O</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>667956</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>3182</v>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Tuyu|Fortuners</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>682508</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>+4497</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>2810</v>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Khakashi Hatake</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>585884</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>2792</v>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ikhram </t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>830337</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>3954</v>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Prince G™</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>742430</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>3395</v>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Yhwach Genryusai</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>600053</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>2787</v>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>NicolasRicko</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>756666</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>3601</v>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Izx Hatake Jr</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>574197</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>2663</v>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>ASHBORN™</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>543900</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>2589</v>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heisenberg </t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>570182</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>2642</v>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Tobirama Senju™</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>1280980</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>+52186</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>4812</v>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>ZenithEX</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>871945</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>4152</v>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>§åñÐåïmårµ | Frtners</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>583280</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>2705</v>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Meru™</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>871787</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>4153</v>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Vnzla Anbu |SN</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>1046177</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>+80204</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>3400</v>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Signature</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>639656</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>3044</v>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Fusion</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>752188</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>3584</v>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Sesshomaru</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>1386739</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>+177</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>6539</v>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>KYO</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>503263</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>2396</v>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>SL41F3RT</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>696672</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>3317</v>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>579158</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>2684</v>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>ShadowRavenX</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>904362</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>4305</v>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>SNC | TemperiTa</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>908740</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>4328</v>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>SmallDino</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>768068</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>3646</v>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>Breaker LITE</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>1130531</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>+101147</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>3440</v>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Snoopy | Kokyotosu</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>798073</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>+903</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>3791</v>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Arya</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>832940</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>3964</v>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Morrissey</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>1112614</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="n">
+        <v>5216</v>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Jonny Brown</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>1287122</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>+91838</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="n">
+        <v>4749</v>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Knightwalker</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>766062</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="n">
+        <v>3619</v>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a fucking ninja </t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>701323</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>3319</v>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Izx Infernity </t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>564491</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="n">
+        <v>2616</v>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Erza Scarlet</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>841211</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>4000</v>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/crew_101.xlsx
+++ b/crew_101.xlsx
@@ -16,6 +16,7 @@
     <sheet name="2026-07-21" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="2026-07-22" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="2026-07-23" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="2026-07-24" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1427,6 +1428,992 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Crew: Shad0w Ninjas (101) | S28 P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-07-24 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Dmg</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Dmg</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Boss Kills</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Kills</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>dogan</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>750938</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>3574</v>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>I Am Dead  @_@</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>734448</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>3498</v>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Yata</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>548662</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>+176</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>2612</v>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>AangEX</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>821854</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>3911</v>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Feirisu</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>719963</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>3431</v>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Wolf †</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>760407</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>3621</v>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>MATHEMATRICK</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>643615</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>+1095</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>3058</v>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>BlacKAkiresu O</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>667956</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>3182</v>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Tuyu|Fortuners</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>728158</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>+45650</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>2810</v>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Khakashi Hatake</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>585884</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>2792</v>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ikhram </t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>830337</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>3954</v>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Prince G™</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>751869</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>+9439</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>3395</v>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Yhwach Genryusai</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>600053</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>2787</v>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>NicolasRicko</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>756666</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>3601</v>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Izx Hatake Jr</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>574197</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>2663</v>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>ASHBORN™</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>543900</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>2589</v>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heisenberg </t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>570182</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>2642</v>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Tobirama Senju™</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>1366939</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>+85959</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>4812</v>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>ZenithEX</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>871945</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>4152</v>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>§åñÐåïmårµ | Frtners</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>583280</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>2705</v>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Meru™</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>871787</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>4153</v>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Vnzla Anbu |SN</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>1126961</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>+80784</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>3400</v>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Signature</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>639656</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>3044</v>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Fusion</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>752188</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>3584</v>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Sesshomaru</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>1386739</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>6539</v>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>KYO</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>503263</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>2396</v>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>SL41F3RT</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>696672</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>3317</v>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>579158</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>2684</v>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>ShadowRavenX</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>904362</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>4305</v>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>SNC | TemperiTa</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>908740</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>4328</v>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>SmallDino</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>768068</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>3646</v>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>Breaker LITE</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>1182289</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>+51758</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>3440</v>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Snoopy | Kokyotosu</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>850062</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>+51989</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>3791</v>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Arya</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>832940</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>3964</v>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Morrissey</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>1112614</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="n">
+        <v>5216</v>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Jonny Brown</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>1342778</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>+55656</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="n">
+        <v>4749</v>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Knightwalker</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>769695</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>+3633</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="n">
+        <v>3619</v>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a fucking ninja </t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>701323</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>3319</v>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Izx Infernity </t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>564491</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="n">
+        <v>2616</v>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Erza Scarlet</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>841211</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>4000</v>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/crew_101.xlsx
+++ b/crew_101.xlsx
@@ -17,6 +17,7 @@
     <sheet name="2026-07-22" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="2026-07-23" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="2026-07-24" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="2026-07-25" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2414,6 +2415,992 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Crew: Shad0w Ninjas (101) | S28 P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-07-25 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Dmg</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Dmg</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Boss Kills</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Kills</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>dogan</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>750938</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>3574</v>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>I Am Dead  @_@</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>734448</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>3498</v>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Yata</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>548662</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>2612</v>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>AangEX</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>821854</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>3911</v>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Feirisu</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>719963</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>3431</v>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Wolf †</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>760407</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>3621</v>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>MATHEMATRICK</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>643615</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>3058</v>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>BlacKAkiresu O</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>667956</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>3182</v>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Tuyu|Fortuners</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>728158</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>2810</v>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Khakashi Hatake</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>585884</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>2792</v>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ikhram </t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>830337</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>3954</v>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Prince G™</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>751869</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>3395</v>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Yhwach Genryusai</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>611421</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>+11368</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>2787</v>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>NicolasRicko</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>756666</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>3601</v>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Izx Hatake Jr</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>574197</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>2663</v>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>ASHBORN™</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>555233</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>+11333</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>2589</v>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heisenberg </t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>570182</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>2642</v>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Tobirama Senju™</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>1440365</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>+73426</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>4812</v>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>ZenithEX</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>871945</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>4152</v>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>§åñÐåïmårµ | Frtners</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>583280</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>2705</v>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Meru™</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>871787</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>4153</v>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Vnzla Anbu |SN</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>1213638</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>+86677</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>3400</v>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Signature</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>639656</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>3044</v>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Fusion</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>752188</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>3584</v>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Sesshomaru</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>1386739</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>6539</v>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>KYO</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>503263</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>2396</v>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>SL41F3RT</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>696672</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>3317</v>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>579158</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>2684</v>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>ShadowRavenX</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>904362</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>4305</v>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>SNC | TemperiTa</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>908740</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>4328</v>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>SmallDino</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>768068</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>3646</v>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>Breaker LITE</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>1286083</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>+103794</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>3440</v>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Snoopy | Kokyotosu</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>929802</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>+79740</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>3791</v>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Arya</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>846023</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>+13083</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>3964</v>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Morrissey</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>1112614</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="n">
+        <v>5216</v>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Jonny Brown</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>1437701</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>+94923</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="n">
+        <v>4749</v>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Knightwalker</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>769695</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="n">
+        <v>3619</v>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a fucking ninja </t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>701323</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>3319</v>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Izx Infernity </t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>564491</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="n">
+        <v>2616</v>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Erza Scarlet</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>841211</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>4000</v>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/crew_101.xlsx
+++ b/crew_101.xlsx
@@ -1448,7 +1448,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Crew: Shad0w Ninjas (101) | S28 P1</t>
+          <t>Crew: Shad0w Ninjas (101) | S28 P2</t>
         </is>
       </c>
     </row>
@@ -2434,7 +2434,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Crew: Shad0w Ninjas (101) | S28 P1</t>
+          <t>Crew: Shad0w Ninjas (101) | S28 P2</t>
         </is>
       </c>
     </row>
@@ -6376,7 +6376,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Crew: Shad0w Ninjas (101) | S28 P2</t>
+          <t>Crew: Shad0w Ninjas (101) | S28 P1</t>
         </is>
       </c>
     </row>
@@ -7032,7 +7032,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Crew: Shad0w Ninjas (101) | S28 P1</t>
+          <t>Crew: Shad0w Ninjas (101) | S28 P2</t>
         </is>
       </c>
     </row>
@@ -8018,7 +8018,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Crew: Shad0w Ninjas (101) | S28 P1</t>
+          <t>Crew: Shad0w Ninjas (101) | S28 P2</t>
         </is>
       </c>
     </row>
@@ -9004,7 +9004,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Crew: Shad0w Ninjas (101) | S28 P1</t>
+          <t>Crew: Shad0w Ninjas (101) | S28 P2</t>
         </is>
       </c>
     </row>
@@ -9990,7 +9990,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Crew: Shad0w Ninjas (101) | S28 P1</t>
+          <t>Crew: Shad0w Ninjas (101) | S28 P2</t>
         </is>
       </c>
     </row>
